--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T14:34:29+00:00</t>
+    <t>2026-10-13T17:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T17:29:18+00:00</t>
+    <t>2026-10-17T12:59:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
